--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260727_210307.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260727_210307.xlsx
@@ -5666,7 +5666,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6204,7 +6204,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8644,7 +8644,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260727_210307.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260727_210307.xlsx
@@ -5666,7 +5666,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6204,7 +6204,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260727_210307.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260727_210307.xlsx
@@ -5666,7 +5666,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6204,7 +6204,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8644,7 +8644,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260727_210307.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260727_210307.xlsx
@@ -5666,7 +5666,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6204,7 +6204,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7182,7 +7182,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8644,7 +8644,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
